--- a/Заявки ввод Шесталюк 2026.xlsx
+++ b/Заявки ввод Шесталюк 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1600EB7-968E-483B-B50E-D7F39E89FC9B}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1988C51-BD77-4B13-8405-167BC586E037}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -148,6 +148,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -495,18 +498,20 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="G5" s="6">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" t="s">
@@ -649,7 +654,7 @@
     <row r="16" spans="2:9" ht="26.25">
       <c r="G16" s="5">
         <f>SUM(G5:G12)</f>
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Заявки ввод Шесталюк 2026.xlsx
+++ b/Заявки ввод Шесталюк 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1988C51-BD77-4B13-8405-167BC586E037}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D8F853-B4A3-45DD-A907-5D9E03053E0B}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -536,18 +536,20 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" t="s">
@@ -654,7 +656,7 @@
     <row r="16" spans="2:9" ht="26.25">
       <c r="G16" s="5">
         <f>SUM(G5:G12)</f>
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Заявки ввод Шесталюк 2026.xlsx
+++ b/Заявки ввод Шесталюк 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="85" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78D8F853-B4A3-45DD-A907-5D9E03053E0B}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9AABF80-FCE7-4DBB-A705-8EF1BB5EC20F}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,18 +556,20 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="G8" s="1">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" t="s">
@@ -656,7 +658,7 @@
     <row r="16" spans="2:9" ht="26.25">
       <c r="G16" s="5">
         <f>SUM(G5:G12)</f>
-        <v>55</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/Заявки ввод Шесталюк 2026.xlsx
+++ b/Заявки ввод Шесталюк 2026.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="93" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9AABF80-FCE7-4DBB-A705-8EF1BB5EC20F}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB16C7CE-3870-4104-8EB7-AE0AF2A1C469}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Зааявка от:</t>
   </si>
@@ -57,6 +57,9 @@
     <t>Сургутский район</t>
   </si>
   <si>
+    <t>55 ?</t>
+  </si>
+  <si>
     <t>Нягань</t>
   </si>
   <si>
@@ -66,13 +69,13 @@
     <t>Лангепас</t>
   </si>
   <si>
-    <t>Кондинский</t>
+    <t>Кондинский (ХМАО-Югра)</t>
   </si>
   <si>
     <t>ЮКИОР Х-М</t>
   </si>
   <si>
-    <t>Елец (Липецк обл.)</t>
+    <t>Хакасия</t>
   </si>
 </sst>
 </file>
@@ -104,7 +107,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -114,6 +117,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -139,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -151,6 +160,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -468,7 +478,7 @@
   <dimension ref="B4:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="9.5703125" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
   </cols>
@@ -497,16 +507,16 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>5</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>5</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>12</v>
       </c>
       <c r="G5" s="6">
@@ -517,34 +527,39 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>0</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1"/>
+      <c r="E6" s="7">
+        <v>7</v>
+      </c>
+      <c r="F6" s="7">
+        <v>7</v>
+      </c>
+      <c r="G6" s="1">
+        <v>7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>7</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>7</v>
       </c>
       <c r="G7" s="1">
@@ -553,18 +568,18 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3">
         <v>8</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>8</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>25</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="3">
         <v>25</v>
       </c>
       <c r="G8" s="1">
@@ -573,7 +588,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
         <v>8</v>
@@ -593,57 +608,63 @@
     </row>
     <row r="10" spans="2:9">
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3">
+        <v>19</v>
+      </c>
+      <c r="F11" s="3">
+        <v>19</v>
+      </c>
+      <c r="G11" s="1">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" spans="2:9">
       <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3">
+        <v>30</v>
+      </c>
+      <c r="G12" s="1">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="4"/>
@@ -658,7 +679,7 @@
     <row r="16" spans="2:9" ht="26.25">
       <c r="G16" s="5">
         <f>SUM(G5:G12)</f>
-        <v>88</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Заявки ввод Шесталюк 2026.xlsx
+++ b/Заявки ввод Шесталюк 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="141" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB16C7CE-3870-4104-8EB7-AE0AF2A1C469}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F47F3C78-27B0-4B80-8C0E-3EB12711E9DD}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
     <t>Сургутский район</t>
   </si>
   <si>
-    <t>55 ?</t>
+    <t>Сургут</t>
   </si>
   <si>
     <t>Нягань</t>
@@ -107,7 +107,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -117,12 +117,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -148,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -160,7 +154,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -475,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:I16"/>
+  <dimension ref="B4:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -527,68 +520,65 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7">
-        <v>7</v>
-      </c>
-      <c r="F6" s="7">
-        <v>7</v>
+      <c r="C6" s="3">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3">
+        <v>39</v>
       </c>
       <c r="G6" s="1">
-        <v>7</v>
-      </c>
-      <c r="I6" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
+      <c r="F7" s="3">
         <v>6</v>
       </c>
-      <c r="E7" s="3">
-        <v>7</v>
-      </c>
-      <c r="F7" s="3">
-        <v>7</v>
-      </c>
       <c r="G7" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F8" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3">
         <v>8</v>
@@ -597,89 +587,109 @@
         <v>8</v>
       </c>
       <c r="E9" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:9">
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F10" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F11" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="2:9">
       <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>19</v>
+      </c>
+      <c r="F12" s="3">
+        <v>19</v>
+      </c>
+      <c r="G12" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C13" s="3">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D13" s="3">
         <v>1</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E13" s="3">
         <v>30</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F13" s="3">
         <v>30</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="16" spans="2:9" ht="26.25">
-      <c r="G16" s="5">
-        <f>SUM(G5:G12)</f>
-        <v>159</v>
+    <row r="14" spans="2:9">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="17" spans="7:7" ht="26.25">
+      <c r="G17" s="5">
+        <f>SUM(G5:G13)</f>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/Заявки ввод Шесталюк 2026.xlsx
+++ b/Заявки ввод Шесталюк 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="156" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F47F3C78-27B0-4B80-8C0E-3EB12711E9DD}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="11_924874E5C5FBB6926123EA198B3E8C185103838B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{884E9E47-39FC-4AF6-B2FC-F880C3493C83}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Зааявка от:</t>
   </si>
@@ -66,9 +66,15 @@
     <t>Нефтеюганск</t>
   </si>
   <si>
+    <t>ИТОГО ОБРАБОТАНО:</t>
+  </si>
+  <si>
     <t>Лангепас</t>
   </si>
   <si>
+    <t>атлета</t>
+  </si>
+  <si>
     <t>Кондинский (ХМАО-Югра)</t>
   </si>
   <si>
@@ -76,13 +82,46 @@
   </si>
   <si>
     <t>Хакасия</t>
+  </si>
+  <si>
+    <t>Аксарка</t>
+  </si>
+  <si>
+    <t>Маслянино</t>
+  </si>
+  <si>
+    <t>Муравленко</t>
+  </si>
+  <si>
+    <t>Ноябрьск</t>
+  </si>
+  <si>
+    <t>Новый Уренгой</t>
+  </si>
+  <si>
+    <t>Омск</t>
+  </si>
+  <si>
+    <t>Салехард</t>
+  </si>
+  <si>
+    <t>Северск</t>
+  </si>
+  <si>
+    <t>Омская область (Нововаршавка)</t>
+  </si>
+  <si>
+    <t>Тарко-Сале</t>
+  </si>
+  <si>
+    <t>Тюмень</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +145,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -121,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -138,11 +198,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -154,6 +240,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -468,228 +563,554 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:I17"/>
+  <dimension ref="B2:L30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="9.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:9">
-      <c r="B4" t="s">
+    <row r="2" spans="2:12">
+      <c r="C2" t="s">
         <v>0</v>
       </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="B3" s="10">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="10">
+        <v>2</v>
+      </c>
       <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3">
+        <v>39</v>
+      </c>
+      <c r="G4" s="3">
+        <v>39</v>
+      </c>
+      <c r="H4" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="10">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3">
+        <v>6</v>
+      </c>
+      <c r="H5" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="10">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3">
+        <v>7</v>
+      </c>
+      <c r="H6" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="10">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>25</v>
+      </c>
+      <c r="G7" s="3">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1">
+        <v>33</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="18.75">
+      <c r="B8" s="10">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1">
+        <v>25</v>
+      </c>
+      <c r="J8" s="12"/>
+      <c r="K8" s="13">
+        <f>SUM(H3:H22)</f>
+        <v>302</v>
+      </c>
+      <c r="L8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="10">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="10">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>19</v>
+      </c>
+      <c r="G10" s="3">
+        <v>19</v>
+      </c>
+      <c r="H10" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="10">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>30</v>
+      </c>
+      <c r="G11" s="3">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" s="10">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6</v>
+      </c>
+      <c r="G12" s="3">
+        <v>6</v>
+      </c>
+      <c r="H12" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="10">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3">
+        <v>4</v>
+      </c>
+      <c r="H13" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="10">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>9</v>
+      </c>
+      <c r="G14" s="3">
+        <v>9</v>
+      </c>
+      <c r="H14" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="10">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6</v>
+      </c>
+      <c r="F15" s="3">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="10">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="11">
+        <v>4</v>
+      </c>
+      <c r="E16" s="11">
+        <v>4</v>
+      </c>
+      <c r="F16" s="11">
+        <v>8</v>
+      </c>
+      <c r="G16" s="11">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="10">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="10">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="3">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E18" s="3">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G18" s="3">
+        <v>4</v>
+      </c>
+      <c r="H18" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="10">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="10">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="G20" s="3">
         <v>5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="H20" s="1">
         <v>5</v>
       </c>
-      <c r="E5" s="3">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="10">
+        <v>19</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="3">
         <v>7</v>
       </c>
-      <c r="C6" s="3">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3">
-        <v>39</v>
-      </c>
-      <c r="F6" s="3">
-        <v>39</v>
-      </c>
-      <c r="G6" s="1">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3">
-        <v>6</v>
-      </c>
-      <c r="G7" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="E21" s="3">
         <v>7</v>
       </c>
-      <c r="F8" s="3">
-        <v>7</v>
-      </c>
-      <c r="G8" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="3">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>25</v>
-      </c>
-      <c r="G9" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3">
-        <v>17</v>
-      </c>
-      <c r="F10" s="3">
-        <v>17</v>
-      </c>
-      <c r="G10" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3">
-        <v>9</v>
-      </c>
-      <c r="F11" s="3">
-        <v>9</v>
-      </c>
-      <c r="G11" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>19</v>
-      </c>
-      <c r="F12" s="3">
-        <v>19</v>
-      </c>
-      <c r="G12" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="F21" s="3">
+        <v>15</v>
+      </c>
+      <c r="G21" s="3">
+        <v>15</v>
+      </c>
+      <c r="H21" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="10">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="3">
         <v>1</v>
       </c>
-      <c r="D13" s="3">
+      <c r="E22" s="3">
         <v>1</v>
       </c>
-      <c r="E13" s="3">
-        <v>30</v>
-      </c>
-      <c r="F13" s="3">
-        <v>30</v>
-      </c>
-      <c r="G13" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="17" spans="7:7" ht="26.25">
-      <c r="G17" s="5">
-        <f>SUM(G5:G13)</f>
-        <v>215</v>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="30" spans="2:9" ht="26.25">
+      <c r="H30" s="5">
+        <f>SUM(H3:H15)</f>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
